--- a/outputs/monitor_xlsx/20260327.xlsx
+++ b/outputs/monitor_xlsx/20260327.xlsx
@@ -544,10 +544,6 @@
           <t>-0.68%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.68%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+0.54%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+2.66%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>-0.02%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>-1.69%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>+13.16%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+5.46%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-363.56億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-206.06億</t>
@@ -807,7 +769,6 @@
           <t>-1.88億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>37.26億</t>
@@ -818,8 +779,6 @@
           <t>186.28億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>131.17%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>124.47%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-383.39億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>7842口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8511口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>-32.69億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>7.1億</t>
@@ -1016,10 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2178,6 +2120,112 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7915</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="E19" t="n">
+        <v>88</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-89</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>292</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1419</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-8985</v>
+      </c>
+      <c r="N19" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1615</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3636</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>-410</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1167</v>
+      </c>
+      <c r="H20" t="n">
+        <v>188</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1876</v>
+      </c>
+      <c r="J20" t="n">
+        <v>96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2873</v>
+      </c>
+      <c r="L20" t="n">
+        <v>14104</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-106310</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260327.xlsx
+++ b/outputs/monitor_xlsx/20260327.xlsx
@@ -544,6 +544,10 @@
           <t>-0.68%</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -566,6 +570,10 @@
           <t>+0.68%</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +591,11 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -605,6 +618,10 @@
           <t>+0.54%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -627,6 +644,10 @@
           <t>+2.66%</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -649,6 +670,10 @@
           <t>-0.02%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -671,6 +696,10 @@
           <t>-1.69%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -693,6 +722,10 @@
           <t>+13.16%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -715,6 +748,10 @@
           <t>+5.46%</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -732,14 +769,15 @@
           <t>-363.56億</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-206.06億</t>
+          <t>-213.97億</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1030.29億</t>
+          <t>-1069.85億</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -769,16 +807,19 @@
           <t>-1.88億</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.26億</t>
+          <t>39.75億</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>186.28億</t>
-        </is>
-      </c>
+          <t>198.74億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -793,14 +834,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>131.17%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>124.47%</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,6 +863,11 @@
           <t>-383.39億</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -835,11 +885,15 @@
           <t>7842口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8511口</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -857,24 +911,25 @@
           <t>-32.69億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7.1億</t>
+          <t>5.16億</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>35.51億</t>
+          <t>25.79億</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>None億</t>
+          <t>-7.35億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>None億</t>
+          <t>-147.03億</t>
         </is>
       </c>
     </row>
@@ -921,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-206.06億</t>
+          <t>-213.97億</t>
         </is>
       </c>
     </row>
@@ -933,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1030.29億</t>
+          <t>-1069.85億</t>
         </is>
       </c>
     </row>
@@ -961,6 +1016,10 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -969,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>37.26億</t>
+          <t>39.75億</t>
         </is>
       </c>
     </row>
@@ -981,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>186.28億</t>
+          <t>198.74億</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1059,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.1億</t>
+          <t>5.16億</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1071,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>35.51億</t>
+          <t>25.79億</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>None億</t>
+          <t>-7.35億</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>None億</t>
+          <t>-147.03億</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1100,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1117,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1196,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1261,16 +1313,19 @@
         <v>115798</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-60114</v>
+        <v>-5532</v>
       </c>
       <c r="H4" t="n">
-        <v>-143167</v>
+        <v>-122534</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2000</v>
       </c>
       <c r="J4" t="n">
         <v>1330</v>
       </c>
       <c r="K4" t="n">
-        <v>26756</v>
+        <v>13655</v>
       </c>
       <c r="L4" t="n">
         <v>13520</v>
@@ -1281,12 +1336,7 @@
       <c r="N4" t="n">
         <v>-4554322</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1317,20 +1367,20 @@
       <c r="F5" t="n">
         <v>3897</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <v>-793</v>
+      <c r="G5" s="6" t="n">
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>-654</v>
+        <v>-434</v>
       </c>
       <c r="I5" t="n">
-        <v>-423</v>
+        <v>-2</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>163</v>
+        <v>36</v>
       </c>
       <c r="L5" t="n">
         <v>2841</v>
@@ -1341,12 +1391,7 @@
       <c r="N5" t="n">
         <v>-78881</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1377,20 +1422,20 @@
       <c r="F6" t="n">
         <v>10527</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>-2273</v>
+      <c r="G6" s="6" t="n">
+        <v>1386</v>
       </c>
       <c r="H6" t="n">
-        <v>4495</v>
+        <v>1172</v>
       </c>
       <c r="I6" t="n">
-        <v>281</v>
+        <v>53</v>
       </c>
       <c r="J6" t="n">
-        <v>1171</v>
+        <v>908</v>
       </c>
       <c r="K6" t="n">
-        <v>283</v>
+        <v>366</v>
       </c>
       <c r="L6" t="n">
         <v>5796</v>
@@ -1401,12 +1446,7 @@
       <c r="N6" t="n">
         <v>-649361</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1437,20 +1477,20 @@
       <c r="F7" t="n">
         <v>33883</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>-11136</v>
+      <c r="G7" s="6" t="n">
+        <v>373</v>
       </c>
       <c r="H7" t="n">
-        <v>-24696</v>
+        <v>-24521</v>
       </c>
       <c r="I7" t="n">
-        <v>381</v>
+        <v>-144</v>
       </c>
       <c r="J7" t="n">
-        <v>3365</v>
+        <v>2115</v>
       </c>
       <c r="K7" t="n">
-        <v>112</v>
+        <v>475</v>
       </c>
       <c r="L7" t="n">
         <v>26385</v>
@@ -1461,12 +1501,7 @@
       <c r="N7" t="n">
         <v>-6483131</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1475,12 +1510,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1489,44 +1524,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
+        <v>1655</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-1.19</v>
       </c>
       <c r="F8" t="n">
-        <v>159719</v>
+        <v>4485</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>24119</v>
+        <v>547</v>
       </c>
       <c r="H8" t="n">
-        <v>-62942</v>
+        <v>868</v>
       </c>
       <c r="I8" t="n">
-        <v>-6084</v>
+        <v>147</v>
       </c>
       <c r="J8" t="n">
-        <v>-32251</v>
+        <v>581</v>
       </c>
       <c r="K8" t="n">
-        <v>2655</v>
+        <v>232</v>
       </c>
       <c r="L8" t="n">
-        <v>119839</v>
+        <v>2290</v>
       </c>
       <c r="M8" t="n">
-        <v>519357</v>
+        <v>9436</v>
       </c>
       <c r="N8" t="n">
-        <v>-1124200</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140209</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1535,12 +1565,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1549,44 +1579,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2910</v>
+        <v>1615</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-1.19</v>
+        <v>-1.52</v>
       </c>
       <c r="F9" t="n">
-        <v>2066</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>-484</v>
+        <v>3636</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>141</v>
       </c>
       <c r="H9" t="n">
-        <v>546</v>
+        <v>-507</v>
       </c>
       <c r="I9" t="n">
-        <v>116</v>
+        <v>366</v>
       </c>
       <c r="J9" t="n">
-        <v>442</v>
+        <v>878</v>
       </c>
       <c r="K9" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="L9" t="n">
-        <v>1886</v>
+        <v>2873</v>
       </c>
       <c r="M9" t="n">
-        <v>7862</v>
+        <v>11231</v>
       </c>
       <c r="N9" t="n">
-        <v>-89564</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106310</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1595,12 +1620,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1609,44 +1634,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2115</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1.68</v>
+        <v>2910</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>-1.19</v>
       </c>
       <c r="F10" t="n">
-        <v>2494</v>
+        <v>2066</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-152</v>
+        <v>-349</v>
       </c>
       <c r="H10" t="n">
-        <v>-1136</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>-77</v>
       </c>
       <c r="J10" t="n">
-        <v>1144</v>
+        <v>426</v>
       </c>
       <c r="K10" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="L10" t="n">
-        <v>4025</v>
+        <v>1886</v>
       </c>
       <c r="M10" t="n">
-        <v>16604</v>
+        <v>7862</v>
       </c>
       <c r="N10" t="n">
-        <v>-19454</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89564</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1655,58 +1675,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1720</v>
+        <v>2115</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="F11" t="n">
-        <v>5080</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>-212</v>
+        <v>2494</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>195</v>
       </c>
       <c r="H11" t="n">
-        <v>-34</v>
+        <v>-841</v>
       </c>
       <c r="I11" t="n">
-        <v>28</v>
+        <v>-68</v>
       </c>
       <c r="J11" t="n">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="K11" t="n">
-        <v>-239</v>
+        <v>24</v>
       </c>
       <c r="L11" t="n">
-        <v>172</v>
+        <v>4025</v>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>16604</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-19454</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1715,55 +1730,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>396.5</v>
+        <v>7915</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-3.53</v>
+        <v>-2.82</v>
       </c>
       <c r="F12" t="n">
-        <v>1968</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>-215</v>
+        <v>88</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>2804</v>
+        <v>85</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-10</v>
       </c>
       <c r="J12" t="n">
-        <v>2120</v>
+        <v>-76</v>
       </c>
       <c r="K12" t="n">
-        <v>-42</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>-389</v>
+        <v>292</v>
       </c>
       <c r="M12" t="n">
-        <v>-1174</v>
+        <v>1127</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8985</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1772,58 +1785,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1655</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-1.19</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>4485</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-577</v>
+        <v>-212</v>
       </c>
       <c r="H13" t="n">
-        <v>453</v>
+        <v>-34</v>
       </c>
       <c r="I13" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="J13" t="n">
-        <v>664</v>
+        <v>577</v>
       </c>
       <c r="K13" t="n">
-        <v>87</v>
+        <v>-239</v>
       </c>
       <c r="L13" t="n">
-        <v>2290</v>
+        <v>172</v>
       </c>
       <c r="M13" t="n">
-        <v>9436</v>
+        <v>-1</v>
       </c>
       <c r="N13" t="n">
-        <v>-140209</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1832,12 +1840,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1846,44 +1854,36 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>854</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>5.56</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>1017</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>94</v>
+        <v>3871</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>-215</v>
       </c>
       <c r="H14" t="n">
-        <v>-171</v>
-      </c>
-      <c r="I14" t="n">
-        <v>14</v>
+        <v>2804</v>
       </c>
       <c r="J14" t="n">
-        <v>-18</v>
+        <v>2120</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>-42</v>
       </c>
       <c r="L14" t="n">
-        <v>-64</v>
+        <v>-389</v>
       </c>
       <c r="M14" t="n">
-        <v>-482</v>
+        <v>-1174</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3.09</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>5559</v>
+        <v>1350</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>924</v>
@@ -1938,12 +1938,7 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1952,280 +1947,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>260</v>
+        <v>1600</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2.77</v>
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>3568</v>
+        <v>904</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>-8</v>
+        <v>-116</v>
       </c>
       <c r="H16" t="n">
-        <v>621</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-3</v>
+        <v>256</v>
       </c>
       <c r="J16" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="K16" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="L16" t="n">
-        <v>6492</v>
+        <v>164</v>
       </c>
       <c r="M16" t="n">
-        <v>25009</v>
+        <v>-159</v>
       </c>
       <c r="N16" t="n">
-        <v>-59038</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>華夏</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-2.62</v>
-      </c>
-      <c r="F17" t="n">
-        <v>45934</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-6090</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-134</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>85</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8558</v>
-      </c>
-      <c r="M17" t="n">
-        <v>29991</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-145189</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>22.15</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F18" t="n">
-        <v>15569</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>1407</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5164</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>81</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7985</v>
-      </c>
-      <c r="M18" t="n">
-        <v>32733</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-99020</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>7915</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>-2.82</v>
-      </c>
-      <c r="E19" t="n">
-        <v>88</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" t="n">
-        <v>59</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-89</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>292</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1419</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-8985</v>
-      </c>
-      <c r="N19" t="n">
-        <v>22.95</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1615</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3636</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>-410</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-1167</v>
-      </c>
-      <c r="H20" t="n">
-        <v>188</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1876</v>
-      </c>
-      <c r="J20" t="n">
-        <v>96</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2873</v>
-      </c>
-      <c r="L20" t="n">
-        <v>14104</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-106310</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260327.xlsx
+++ b/outputs/monitor_xlsx/20260327.xlsx
@@ -544,10 +544,6 @@
           <t>-0.68%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.68%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>+0.54%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+2.66%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>-0.02%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>-1.69%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>+13.16%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>+5.46%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-363.56億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-213.97億</t>
@@ -807,7 +769,6 @@
           <t>-1.88億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>39.75億</t>
@@ -818,8 +779,6 @@
           <t>198.74億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>124.47%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-383.39億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>7842口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8511口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>-32.69億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>5.16億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1994,6 +1937,45 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>372</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1192</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-46</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7744</v>
+      </c>
+      <c r="L17" t="n">
+        <v>40066</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22125</v>
+      </c>
+      <c r="N17" t="n">
+        <v>15.26</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260327.xlsx
+++ b/outputs/monitor_xlsx/20260327.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,39 +1245,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>75</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-1.06</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>115798</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-5532</v>
+        <v>-60114</v>
       </c>
       <c r="H4" t="n">
-        <v>-122534</v>
+        <v>-203280</v>
       </c>
       <c r="I4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1330</v>
       </c>
       <c r="K4" t="n">
-        <v>13655</v>
+        <v>26756</v>
       </c>
       <c r="L4" t="n">
         <v>13520</v>
       </c>
       <c r="M4" t="n">
-        <v>53358</v>
+        <v>66878</v>
       </c>
       <c r="N4" t="n">
         <v>-4554322</v>
       </c>
+      <c r="O4" t="n">
+        <v>-1.71</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1301,39 +1303,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>865</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-3.24</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>3897</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>26</v>
+      <c r="G5" s="7" t="n">
+        <v>-793</v>
       </c>
       <c r="H5" t="n">
-        <v>-434</v>
+        <v>-1447</v>
       </c>
       <c r="I5" t="n">
-        <v>-2</v>
+        <v>-423</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>-415</v>
       </c>
       <c r="K5" t="n">
-        <v>36</v>
+        <v>163</v>
       </c>
       <c r="L5" t="n">
         <v>2841</v>
       </c>
       <c r="M5" t="n">
-        <v>11263</v>
+        <v>14104</v>
       </c>
       <c r="N5" t="n">
         <v>-78881</v>
       </c>
+      <c r="O5" t="n">
+        <v>-6.03</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1356,39 +1361,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1510</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-0.33</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>10527</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>1386</v>
+      <c r="G6" s="7" t="n">
+        <v>-2273</v>
       </c>
       <c r="H6" t="n">
-        <v>1172</v>
+        <v>2222</v>
       </c>
       <c r="I6" t="n">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="J6" t="n">
-        <v>908</v>
+        <v>1453</v>
       </c>
       <c r="K6" t="n">
-        <v>366</v>
+        <v>283</v>
       </c>
       <c r="L6" t="n">
         <v>5796</v>
       </c>
       <c r="M6" t="n">
-        <v>22618</v>
+        <v>28414</v>
       </c>
       <c r="N6" t="n">
         <v>-649361</v>
       </c>
+      <c r="O6" t="n">
+        <v>8.109999999999999</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1411,39 +1419,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1820</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-1.09</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>33883</v>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>373</v>
+      <c r="G7" s="7" t="n">
+        <v>-11136</v>
       </c>
       <c r="H7" t="n">
-        <v>-24521</v>
+        <v>-35832</v>
       </c>
       <c r="I7" t="n">
-        <v>-144</v>
+        <v>381</v>
       </c>
       <c r="J7" t="n">
-        <v>2115</v>
+        <v>3746</v>
       </c>
       <c r="K7" t="n">
-        <v>475</v>
+        <v>112</v>
       </c>
       <c r="L7" t="n">
         <v>26385</v>
       </c>
       <c r="M7" t="n">
-        <v>105565</v>
+        <v>131950</v>
       </c>
       <c r="N7" t="n">
         <v>-6483131</v>
       </c>
+      <c r="O7" t="n">
+        <v>-2.54</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1466,39 +1477,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1655</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-1.19</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>4485</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>547</v>
+      <c r="G8" s="7" t="n">
+        <v>-577</v>
       </c>
       <c r="H8" t="n">
-        <v>868</v>
+        <v>-124</v>
       </c>
       <c r="I8" t="n">
-        <v>147</v>
+        <v>54</v>
       </c>
       <c r="J8" t="n">
-        <v>581</v>
+        <v>718</v>
       </c>
       <c r="K8" t="n">
-        <v>232</v>
+        <v>87</v>
       </c>
       <c r="L8" t="n">
         <v>2290</v>
       </c>
       <c r="M8" t="n">
-        <v>9436</v>
+        <v>11726</v>
       </c>
       <c r="N8" t="n">
         <v>-140209</v>
       </c>
+      <c r="O8" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1521,39 +1535,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1615</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>-1.52</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>3636</v>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>141</v>
+      <c r="G9" s="7" t="n">
+        <v>-410</v>
       </c>
       <c r="H9" t="n">
-        <v>-507</v>
+        <v>-1167</v>
       </c>
       <c r="I9" t="n">
-        <v>366</v>
+        <v>188</v>
       </c>
       <c r="J9" t="n">
-        <v>878</v>
+        <v>1876</v>
       </c>
       <c r="K9" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="L9" t="n">
         <v>2873</v>
       </c>
       <c r="M9" t="n">
-        <v>11231</v>
+        <v>14104</v>
       </c>
       <c r="N9" t="n">
         <v>-106310</v>
       </c>
+      <c r="O9" t="n">
+        <v>8.77</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1576,39 +1593,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2910</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-1.19</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>2066</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-349</v>
+        <v>-484</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="I10" t="n">
-        <v>-77</v>
+        <v>116</v>
       </c>
       <c r="J10" t="n">
-        <v>426</v>
+        <v>559</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="L10" t="n">
         <v>1886</v>
       </c>
       <c r="M10" t="n">
-        <v>7862</v>
+        <v>9748</v>
       </c>
       <c r="N10" t="n">
         <v>-89564</v>
       </c>
+      <c r="O10" t="n">
+        <v>12.39</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1631,39 +1651,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>2115</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>1.68</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>2494</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <v>195</v>
+      <c r="G11" s="7" t="n">
+        <v>-152</v>
       </c>
       <c r="H11" t="n">
-        <v>-841</v>
+        <v>-1288</v>
       </c>
       <c r="I11" t="n">
-        <v>-68</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>562</v>
+        <v>1163</v>
       </c>
       <c r="K11" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L11" t="n">
         <v>4025</v>
       </c>
       <c r="M11" t="n">
-        <v>16604</v>
+        <v>20629</v>
       </c>
       <c r="N11" t="n">
         <v>-19454</v>
       </c>
+      <c r="O11" t="n">
+        <v>9.529999999999999</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1686,39 +1709,42 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>7915</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>-2.82</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>88</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="I12" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="J12" t="n">
-        <v>-76</v>
+        <v>-89</v>
       </c>
       <c r="K12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>292</v>
       </c>
       <c r="M12" t="n">
-        <v>1127</v>
+        <v>1419</v>
       </c>
       <c r="N12" t="n">
         <v>-8985</v>
       </c>
+      <c r="O12" t="n">
+        <v>22.95</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1741,26 +1767,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>-212</v>
       </c>
       <c r="H13" t="n">
-        <v>-34</v>
+        <v>-246</v>
       </c>
       <c r="I13" t="n">
         <v>28</v>
       </c>
       <c r="J13" t="n">
-        <v>577</v>
+        <v>605</v>
       </c>
       <c r="K13" t="n">
         <v>-239</v>
@@ -1769,11 +1795,14 @@
         <v>172</v>
       </c>
       <c r="M13" t="n">
-        <v>-1</v>
+        <v>171</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1796,20 +1825,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>-215</v>
       </c>
       <c r="H14" t="n">
-        <v>2804</v>
+        <v>2589</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>2120</v>
@@ -1821,11 +1853,14 @@
         <v>-389</v>
       </c>
       <c r="M14" t="n">
-        <v>-1174</v>
+        <v>-1563</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1848,26 +1883,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>924</v>
       </c>
       <c r="H15" t="n">
-        <v>-3233</v>
+        <v>-2309</v>
       </c>
       <c r="I15" t="n">
         <v>346</v>
       </c>
       <c r="J15" t="n">
-        <v>4683</v>
+        <v>5028</v>
       </c>
       <c r="K15" t="n">
         <v>23</v>
@@ -1876,11 +1911,14 @@
         <v>-86</v>
       </c>
       <c r="M15" t="n">
-        <v>-291</v>
+        <v>-377</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1903,20 +1941,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>-116</v>
       </c>
       <c r="H16" t="n">
-        <v>256</v>
+        <v>140</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-10</v>
@@ -1928,11 +1969,14 @@
         <v>164</v>
       </c>
       <c r="M16" t="n">
-        <v>-159</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1950,32 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>372</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="7" t="n">
         <v>6.44</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="6" t="n">
         <v>1192</v>
       </c>
-      <c r="G17" t="n">
-        <v>-46</v>
+      <c r="G17" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="H17" t="n">
+        <v>26</v>
       </c>
       <c r="I17" t="n">
-        <v>-3</v>
+        <v>-1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-4</v>
       </c>
       <c r="K17" t="n">
+        <v>89</v>
+      </c>
+      <c r="L17" t="n">
         <v>7744</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>40066</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-22125</v>
       </c>
-      <c r="N17" t="n">
-        <v>15.26</v>
+      <c r="O17" t="n">
+        <v>13.87</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260327.xlsx
+++ b/outputs/monitor_xlsx/20260327.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2036,6 +2036,165 @@
         <v>13.87</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1585</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7673</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>545</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-3995</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-785</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-1407</v>
+      </c>
+      <c r="K18" t="n">
+        <v>324</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6141</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30985</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400975</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-7.32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>505</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5779</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-1314</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3575</v>
+      </c>
+      <c r="I19" t="n">
+        <v>174</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2052</v>
+      </c>
+      <c r="K19" t="n">
+        <v>144</v>
+      </c>
+      <c r="L19" t="n">
+        <v>31055</v>
+      </c>
+      <c r="M19" t="n">
+        <v>158854</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393879</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>561</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25431</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>-2526</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2944</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1180</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5028</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1102</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9212</v>
+      </c>
+      <c r="M20" t="n">
+        <v>47108</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-160990</v>
+      </c>
+      <c r="O20" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
